--- a/labs/lab-06-custom-skills-calendar/data/BrightPath_Interview_Schedule.xlsx
+++ b/labs/lab-06-custom-skills-calendar/data/BrightPath_Interview_Schedule.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About_This_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interviews" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Interviews" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="About_This_Data" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prompt_Log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
@@ -70,13 +70,13 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -464,203 +464,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BrightPath Talent Solutions — Interview Schedule (6 - 17 July 2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>All organisations, people, IDs and values in this workbook are FICTIONAL training data created for the Microsoft 365 Copilot for Excel course (C34). Any resemblance to a real company or person is coincidental.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Purpose: one row per candidate interview booked by BrightPath recruiters for two weeks in July 2026. Use it in Lab 6 to build a custom Copilot skill, interview-calendar, that turns this list into a weekly calendar and flags clashes. Candidate names are not stored - only a reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Sheet / Column</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Meaning</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Interview_ID</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Unique key (INT-001 ...).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Candidate_Ref</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Pseudonymised candidate reference.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Role / Client</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Job and hiring client.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Interviewer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>BrightPath recruiter running the interview.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Interview_Date / Start_Time</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Date / hh:mm</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>When the interview starts (24-hour clock).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Duration_Min</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Minutes</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>30, 45 or 60.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Mode / Room</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Onsite interviews use the Orchid Room or Lotus Room; Video interviews use Teams.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Clash rule</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Rule</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>A clash is two interviews that overlap in time with the same Interviewer, or two Onsite interviews that overlap in the same Room.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A2:C2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:J42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -754,10 +557,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.375</v>
       </c>
       <c r="H2" t="n">
@@ -800,10 +603,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="H3" t="n">
@@ -846,10 +649,10 @@
           <t>Priya Nair</t>
         </is>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H4" t="n">
@@ -892,10 +695,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H5" t="n">
@@ -938,10 +741,10 @@
           <t>Daniel Tan</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H6" t="n">
@@ -984,10 +787,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="2" t="n">
         <v>0.625</v>
       </c>
       <c r="H7" t="n">
@@ -1030,10 +833,10 @@
           <t>Siti Hamid</t>
         </is>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="1" t="n">
         <v>46209</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="2" t="n">
         <v>0.6875</v>
       </c>
       <c r="H8" t="n">
@@ -1076,10 +879,10 @@
           <t>Priya Nair</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="2" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="H9" t="n">
@@ -1122,10 +925,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H10" t="n">
@@ -1168,10 +971,10 @@
           <t>Kevin Ong</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H11" t="n">
@@ -1214,10 +1017,10 @@
           <t>Kevin Ong</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="2" t="n">
         <v>0.5520833333333334</v>
       </c>
       <c r="H12" t="n">
@@ -1260,10 +1063,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="1" t="n">
         <v>46210</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="2" t="n">
         <v>0.625</v>
       </c>
       <c r="H13" t="n">
@@ -1306,10 +1109,10 @@
           <t>Daniel Tan</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="2" t="n">
         <v>0.5208333333333334</v>
       </c>
       <c r="H14" t="n">
@@ -1352,10 +1155,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="2" t="n">
         <v>0.5208333333333334</v>
       </c>
       <c r="H15" t="n">
@@ -1398,10 +1201,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="2" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H16" t="n">
@@ -1444,10 +1247,10 @@
           <t>Siti Hamid</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="2" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H17" t="n">
@@ -1490,10 +1293,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="1" t="n">
         <v>46211</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H18" t="n">
@@ -1536,10 +1339,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="2" t="n">
         <v>0.4375</v>
       </c>
       <c r="H19" t="n">
@@ -1582,10 +1385,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="2" t="n">
         <v>0.4479166666666667</v>
       </c>
       <c r="H20" t="n">
@@ -1628,10 +1431,10 @@
           <t>Kevin Ong</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="1" t="n">
         <v>46212</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="H21" t="n">
@@ -1674,10 +1477,10 @@
           <t>Priya Nair</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="2" t="n">
         <v>0.3958333333333333</v>
       </c>
       <c r="H22" t="n">
@@ -1720,10 +1523,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="2" t="n">
         <v>0.5</v>
       </c>
       <c r="H23" t="n">
@@ -1766,10 +1569,10 @@
           <t>Daniel Tan</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="1" t="n">
         <v>46213</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="2" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="H24" t="n">
@@ -1812,10 +1615,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="2" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="H25" t="n">
@@ -1858,10 +1661,10 @@
           <t>Kevin Ong</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="2" t="n">
         <v>0.5625</v>
       </c>
       <c r="H26" t="n">
@@ -1904,10 +1707,10 @@
           <t>Priya Nair</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="1" t="n">
         <v>46216</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="2" t="n">
         <v>0.6041666666666666</v>
       </c>
       <c r="H27" t="n">
@@ -1950,10 +1753,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="1" t="n">
         <v>46217</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H28" t="n">
@@ -1996,10 +1799,10 @@
           <t>Kevin Ong</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="1" t="n">
         <v>46217</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="2" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="H29" t="n">
@@ -2042,10 +1845,10 @@
           <t>Priya Nair</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="1" t="n">
         <v>46217</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="2" t="n">
         <v>0.6458333333333334</v>
       </c>
       <c r="H30" t="n">
@@ -2088,10 +1891,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G31" s="2" t="n">
         <v>0.4375</v>
       </c>
       <c r="H31" t="n">
@@ -2134,10 +1937,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="2" t="n">
         <v>0.4791666666666667</v>
       </c>
       <c r="H32" t="n">
@@ -2180,10 +1983,10 @@
           <t>Siti Hamid</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="2" t="n">
         <v>0.5625</v>
       </c>
       <c r="H33" t="n">
@@ -2226,10 +2029,10 @@
           <t>Siti Hamid</t>
         </is>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="1" t="n">
         <v>46218</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="2" t="n">
         <v>0.6041666666666666</v>
       </c>
       <c r="H34" t="n">
@@ -2272,10 +2075,10 @@
           <t>Aisha Rahman</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="2" t="n">
         <v>0.4166666666666667</v>
       </c>
       <c r="H35" t="n">
@@ -2318,10 +2121,10 @@
           <t>Daniel Tan</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H36" t="n">
@@ -2364,10 +2167,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="2" t="n">
         <v>0.625</v>
       </c>
       <c r="H37" t="n">
@@ -2410,10 +2213,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="1" t="n">
         <v>46219</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="2" t="n">
         <v>0.6875</v>
       </c>
       <c r="H38" t="n">
@@ -2456,10 +2259,10 @@
           <t>Kevin Ong</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H39" t="n">
@@ -2502,10 +2305,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="2" t="n">
         <v>0.5416666666666666</v>
       </c>
       <c r="H40" t="n">
@@ -2548,10 +2351,10 @@
           <t>Marcus Lim</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="2" t="n">
         <v>0.5833333333333334</v>
       </c>
       <c r="H41" t="n">
@@ -2594,10 +2397,10 @@
           <t>Daniel Tan</t>
         </is>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="1" t="n">
         <v>46220</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="G42" s="2" t="n">
         <v>0.625</v>
       </c>
       <c r="H42" t="n">
@@ -2619,6 +2422,203 @@
   <tableParts count="1">
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>BrightPath Talent Solutions — Interview Schedule (6 - 17 July 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="48" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>All organisations, people, IDs and values in this workbook are FICTIONAL training data created for the Microsoft 365 Copilot for Excel course (C34). Any resemblance to a real company or person is coincidental.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="48" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Purpose: one row per candidate interview booked by BrightPath recruiters for two weeks in July 2026. Use it in Lab 6 to build a custom Copilot skill, interview-calendar, that turns this list into a weekly calendar and flags clashes. Candidate names are not stored - only a reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Sheet / Column</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Meaning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Interview_ID</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Unique key (INT-001 ...).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Candidate_Ref</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Pseudonymised candidate reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Role / Client</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Job and hiring client.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Interviewer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>BrightPath recruiter running the interview.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Interview_Date / Start_Time</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Date / hh:mm</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>When the interview starts (24-hour clock).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Duration_Min</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Minutes</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>30, 45 or 60.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Mode / Room</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Onsite interviews use the Orchid Room or Lotus Room; Video interviews use Teams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Clash rule</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>A clash is two interviews that overlap in time with the same Interviewer, or two Onsite interviews that overlap in the same Room.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2640,32 +2640,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Mode (Chat only / Plan / Allow editing)</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Prompt</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>What Copilot did</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>How I verified</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>Decision (Keep / Revise / Undo)</t>
         </is>
